--- a/data/trans_camb/POLIPATOLOGIA_Lim_2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_2-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,33</t>
+          <t>-0,67; 2,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 8,44</t>
+          <t>0,76; 8,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 5,46</t>
+          <t>-0,25; 6,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 16,56</t>
+          <t>4,62; 16,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,35</t>
+          <t>-0,18; 3,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 10,14</t>
+          <t>3,27; 9,9</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-68,77; 790,48</t>
+          <t>-74,34; 803,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 2083,69</t>
+          <t>-13,44; 2463,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 208,15</t>
+          <t>-9,47; 237,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89,88; 640,68</t>
+          <t>90,73; 628,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 212,78</t>
+          <t>-11,12; 199,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>115,72; 589,69</t>
+          <t>103,01; 587,7</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 1,69</t>
+          <t>-2,36; 2,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 5,59</t>
+          <t>-0,38; 5,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 2,25</t>
+          <t>-3,48; 2,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 9,47</t>
+          <t>0,49; 9,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,22</t>
+          <t>-2,03; 1,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 7,11</t>
+          <t>1,51; 7,1</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,0; 71,5</t>
+          <t>-54,14; 84,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 196,87</t>
+          <t>-14,56; 201,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,85; 42,99</t>
+          <t>-41,35; 39,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 164,88</t>
+          <t>6,9; 166,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,88; 27,51</t>
+          <t>-35,17; 32,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,87; 158,81</t>
+          <t>24,34; 158,06</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,57</t>
+          <t>-2,66; 2,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 6,58</t>
+          <t>0,4; 6,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,1; -1,72</t>
+          <t>-9,47; -1,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 5,03</t>
+          <t>-4,34; 5,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; -0,54</t>
+          <t>-5,28; -0,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,9</t>
+          <t>-0,74; 4,82</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,04; 64,21</t>
+          <t>-38,29; 57,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,11; 154,33</t>
+          <t>4,99; 145,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,31; -13,04</t>
+          <t>-52,74; -12,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,24; 36,1</t>
+          <t>-24,34; 35,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-45,16; -5,55</t>
+          <t>-43,62; -6,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 50,39</t>
+          <t>-6,4; 50,41</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 5,17</t>
+          <t>-3,37; 5,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 7,47</t>
+          <t>-9,37; 7,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 4,03</t>
+          <t>-6,12; 3,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 9,62</t>
+          <t>-0,33; 9,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 3,25</t>
+          <t>-3,22; 3,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 7,02</t>
+          <t>-5,9; 7,09</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 46,67</t>
+          <t>-21,93; 45,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,4; 62,11</t>
+          <t>-56,86; 63,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,87; 19,57</t>
+          <t>-24,38; 16,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 48,39</t>
+          <t>-1,12; 48,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 20,52</t>
+          <t>-16,61; 19,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,92; 41,51</t>
+          <t>-30,18; 41,28</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 3,32</t>
+          <t>-8,2; 3,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 6,98</t>
+          <t>-4,12; 6,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 0,14</t>
+          <t>-12,7; 0,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,56; -0,47</t>
+          <t>-12,25; -0,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,38; -0,12</t>
+          <t>-9,02; -0,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 1,29</t>
+          <t>-7,04; 1,48</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,56; 14,6</t>
+          <t>-28,66; 14,54</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 30,9</t>
+          <t>-13,98; 30,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,28; -0,08</t>
+          <t>-26,16; 0,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,39; -1,29</t>
+          <t>-24,34; -0,97</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,47; 0,03</t>
+          <t>-23,73; -0,12</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 3,82</t>
+          <t>-18,23; 4,48</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-24,47; -9,36</t>
+          <t>-24,78; -9,17</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-28,85; -14,73</t>
+          <t>-29,25; -15,6</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-16,63; -2,22</t>
+          <t>-16,29; -1,61</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-54,02; -13,49</t>
+          <t>-48,87; -12,83</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-17,78; -7,2</t>
+          <t>-18,18; -7,38</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-41,81; -17,32</t>
+          <t>-42,15; -16,87</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-45,33; -19,44</t>
+          <t>-44,64; -19,84</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-52,46; -32,21</t>
+          <t>-52,69; -33,22</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-25,36; -3,79</t>
+          <t>-24,7; -2,39</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-80,96; -22,17</t>
+          <t>-76,81; -21,4</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-30,39; -13,51</t>
+          <t>-30,57; -13,28</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-71,8; -30,64</t>
+          <t>-71,59; -30,53</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-23,49; -6,76</t>
+          <t>-23,61; -6,8</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-30,66; -14,77</t>
+          <t>-29,91; -14,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-22,52; -8,54</t>
+          <t>-22,75; -8,95</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-14,38; -4,43</t>
+          <t>-15,51; -4,41</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-20,81; -9,88</t>
+          <t>-20,97; -9,72</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-19,97; -10,32</t>
+          <t>-19,87; -10,83</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-33,82; -11,16</t>
+          <t>-33,77; -10,71</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-43,16; -23,96</t>
+          <t>-43,02; -24,84</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-28,08; -11,35</t>
+          <t>-28,23; -12,15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-17,8; -6,12</t>
+          <t>-18,87; -5,73</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-27,67; -14,13</t>
+          <t>-27,35; -13,67</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-26,19; -14,76</t>
+          <t>-26,09; -15,31</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,75; -0,2</t>
+          <t>-3,79; -0,37</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 2,42</t>
+          <t>-3,43; 2,6</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,66; -1,28</t>
+          <t>-5,43; -1,12</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 3,53</t>
+          <t>-5,15; 3,41</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,16; -1,38</t>
+          <t>-4,24; -1,26</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 2,48</t>
+          <t>-2,71; 2,51</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-20,93; -1,36</t>
+          <t>-21,14; -2,3</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-19,35; 14,75</t>
+          <t>-19,55; 15,55</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-18,8; -4,53</t>
+          <t>-18,12; -3,97</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 12,49</t>
+          <t>-16,96; 12,05</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-17,43; -6,21</t>
+          <t>-17,58; -5,58</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 10,84</t>
+          <t>-11,77; 10,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_Lim_2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_2-Edad-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,75</t>
+          <t>3,52</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,98</t>
+          <t>10,78</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,35</t>
+          <t>6,89</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,28</t>
+          <t>-0,74; 2,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 8,49</t>
+          <t>0,7; 8,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 6,04</t>
+          <t>-0,23; 5,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 16,68</t>
+          <t>5,46; 17,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,21</t>
+          <t>-0,04; 3,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 9,9</t>
+          <t>3,71; 10,31</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>429,92%</t>
+          <t>403,61%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>266,33%</t>
+          <t>287,71%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>279,59%</t>
+          <t>303,47%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-74,34; 803,58</t>
+          <t>-61,7; 751,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 2463,67</t>
+          <t>15,23; 2279,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 237,27</t>
+          <t>-4,8; 222,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90,73; 628,86</t>
+          <t>90,99; 595,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 199,01</t>
+          <t>-2,05; 199,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>103,01; 587,7</t>
+          <t>127,76; 585,64</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,28</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>6,46</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,21</t>
+          <t>4,55</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,09</t>
+          <t>-2,82; 1,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,6</t>
+          <t>-0,38; 5,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 2,23</t>
+          <t>-3,57; 2,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 9,58</t>
+          <t>2,68; 10,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,45</t>
+          <t>-2,37; 1,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 7,1</t>
+          <t>2,44; 7,28</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>87,39%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-54,14; 84,17</t>
+          <t>-57,75; 51,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 201,45</t>
+          <t>-10,16; 195,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,35; 39,19</t>
+          <t>-42,7; 42,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 166,37</t>
+          <t>30,33; 184,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,17; 32,5</t>
+          <t>-37,87; 34,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,34; 158,06</t>
+          <t>36,45; 166,61</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,23</t>
+          <t>2,74</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>2,86</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>2,71</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,42</t>
+          <t>-2,61; 2,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 6,26</t>
+          <t>-0,08; 6,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,47; -1,77</t>
+          <t>-9,18; -2,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 5,01</t>
+          <t>-1,25; 6,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,28; -0,6</t>
+          <t>-5,32; -0,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 4,82</t>
+          <t>0,26; 5,22</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,29; 57,91</t>
+          <t>-37,77; 68,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,99; 145,79</t>
+          <t>-1,66; 144,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,74; -12,18</t>
+          <t>-51,39; -13,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 35,04</t>
+          <t>-7,31; 47,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,62; -6,61</t>
+          <t>-43,25; -6,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 50,41</t>
+          <t>1,35; 53,96</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>5,89</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>5,85</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 5,13</t>
+          <t>-3,12; 4,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 7,77</t>
+          <t>1,82; 10,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 3,3</t>
+          <t>-6,04; 3,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 9,72</t>
+          <t>1,06; 10,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 3,26</t>
+          <t>-3,22; 3,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 7,09</t>
+          <t>2,97; 9,05</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-21,93; 45,81</t>
+          <t>-21,02; 41,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-56,86; 63,86</t>
+          <t>10,5; 92,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-24,38; 16,24</t>
+          <t>-23,54; 18,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 48,29</t>
+          <t>3,95; 51,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 19,93</t>
+          <t>-16,5; 20,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,18; 41,28</t>
+          <t>14,5; 55,47</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-6,15</t>
+          <t>-6,3</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,68</t>
+          <t>-2,92</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 3,31</t>
+          <t>-8,29; 3,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 6,7</t>
+          <t>-4,63; 6,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 0,4</t>
+          <t>-13,49; 0,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,25; -0,58</t>
+          <t>-11,72; 0,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,02; -0,03</t>
+          <t>-9,43; -0,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 1,48</t>
+          <t>-7,04; 1,21</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-13,54%</t>
+          <t>-13,86%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-7,47%</t>
+          <t>-8,13%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,66; 14,54</t>
+          <t>-28,68; 14,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 30,07</t>
+          <t>-15,8; 29,56</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-26,16; 0,7</t>
+          <t>-27,73; -0,2</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,34; -0,97</t>
+          <t>-23,51; 0,07</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-23,73; -0,12</t>
+          <t>-24,47; -0,04</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 4,48</t>
+          <t>-17,98; 3,61</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-22,35</t>
+          <t>-22,9</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-30,93</t>
+          <t>-15,12</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-26,71</t>
+          <t>-19,02</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-24,78; -9,17</t>
+          <t>-25,5; -9,72</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-29,25; -15,6</t>
+          <t>-30,05; -15,65</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-16,29; -1,61</t>
+          <t>-16,82; -1,98</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-48,87; -12,83</t>
+          <t>-21,27; -8,74</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-18,18; -7,38</t>
+          <t>-18,14; -7,21</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-42,15; -16,87</t>
+          <t>-23,87; -14,14</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-43,83%</t>
+          <t>-44,92%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-49,92%</t>
+          <t>-24,4%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-46,99%</t>
+          <t>-33,46%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-44,64; -19,84</t>
+          <t>-46,88; -20,65</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-52,69; -33,22</t>
+          <t>-53,27; -33,7</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-24,7; -2,39</t>
+          <t>-25,38; -3,53</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-76,81; -21,4</t>
+          <t>-32,13; -14,71</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-30,57; -13,28</t>
+          <t>-30,87; -13,52</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-71,59; -30,53</t>
+          <t>-39,81; -26,69</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-22,9</t>
+          <t>-22,86</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-9,81</t>
+          <t>-9,92</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-15,13</t>
+          <t>-15,21</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-23,61; -6,8</t>
+          <t>-23,42; -6,83</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-29,91; -14,84</t>
+          <t>-30,91; -15,05</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-22,75; -8,95</t>
+          <t>-21,93; -8,06</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-15,51; -4,41</t>
+          <t>-15,33; -4,19</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-20,97; -9,72</t>
+          <t>-21,41; -10,07</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-19,87; -10,83</t>
+          <t>-19,46; -10,44</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-34,49%</t>
+          <t>-34,43%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-12,49%</t>
+          <t>-12,62%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-20,5%</t>
+          <t>-20,61%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-33,77; -10,71</t>
+          <t>-33,29; -11,21</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-43,02; -24,84</t>
+          <t>-44,55; -24,55</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-28,23; -12,15</t>
+          <t>-27,01; -10,73</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-18,87; -5,73</t>
+          <t>-18,59; -5,63</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-27,35; -13,67</t>
+          <t>-27,93; -14,07</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-26,09; -15,31</t>
+          <t>-25,28; -14,42</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>3,18</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>2,24</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -0,37</t>
+          <t>-3,84; -0,21</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 2,6</t>
+          <t>-0,77; 3,25</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,43; -1,12</t>
+          <t>-5,73; -1,23</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 3,41</t>
+          <t>1,19; 5,39</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,24; -1,26</t>
+          <t>-4,22; -1,42</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 2,51</t>
+          <t>0,81; 3,74</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-21,14; -2,3</t>
+          <t>-21,53; -1,19</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 15,55</t>
+          <t>-4,37; 20,23</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-18,12; -3,97</t>
+          <t>-18,83; -4,3</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 12,05</t>
+          <t>3,9; 19,31</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-17,58; -5,58</t>
+          <t>-17,68; -6,33</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 10,88</t>
+          <t>3,43; 16,74</t>
         </is>
       </c>
     </row>
